--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-del-nuble.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-del-nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1233616-1463-CM26</t>
+          <t>229-432-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,189 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>27067.96</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1375761-56-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>61.981.330-8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Región del Ñuble</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>IGMA CONSULTORES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>10151.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1052231-109-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Región del Ñuble</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>5753.56</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1233616-1463-CM26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Región del Ñuble</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>27851.72</v>
       </c>
     </row>
